--- a/data/annotation/标注表模板.xlsx
+++ b/data/annotation/标注表模板.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +26,39 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font/>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,8 +73,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,554 +444,775 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM3"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col hidden="1" outlineLevel="1" width="14" customWidth="1" min="2" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col hidden="1" outlineLevel="1" width="14" customWidth="1" min="8" max="14"/>
+    <col hidden="1" outlineLevel="1" width="14" customWidth="1" min="15" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col hidden="1" outlineLevel="1" width="14" customWidth="1" min="36" max="37"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="14" customWidth="1" min="39" max="39"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>sample_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>operator_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>thickness_mm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>glass_type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>quality_mode</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>x0_95_nm</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>iso_t_pct</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ccp_value</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ccp_is_calibrated</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>stress_image_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>stress_image_sha256</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>condition_note</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>baseline_zone_temps_c</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>baseline_zone_roles</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>baseline_temp_upper_c</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>baseline_temp_lower_c</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>baseline_convection_speed</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>baseline_convection_ratio_upper_lower</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>baseline_oscillation_speed</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>baseline_oscillation_amplitude</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>baseline_heating_duration_s</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>final_zone_temps_c</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>final_zone_roles</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>final_temp_upper_c</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>final_temp_lower_c</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>final_convection_speed</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>final_convection_ratio_upper_lower</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>final_oscillation_speed</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>final_oscillation_amplitude</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>final_heating_duration_s</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="2" t="inlineStr">
         <is>
           <t>expert_quality_grade</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="2" t="inlineStr">
         <is>
           <t>rationale</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="2" t="inlineStr">
         <is>
           <t>cause_tag</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>is_ground_truth</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>repeat_group_id</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="3" t="inlineStr">
         <is>
           <t>measured_quality_grade</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="3" t="inlineStr">
         <is>
           <t>measured_energy_kwh</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>示例-说明行(勿删)</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜时间</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜工号</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜产线/班次</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜厚度mm</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜品类</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜质量模式</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜X0.95(nm)</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜IsoT%</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜CCP</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜CCP已标定</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜应力斑图路径</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜图像哈希</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜工况备注</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜基准分区温度℃</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜基准分区角色</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜基准上炉温℃</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜基准下炉温℃</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜基准对流风速</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜基准对流配比</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜基准摆动速度</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜基准摆动幅度</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜基准加热时长s</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜最终分区温度℃</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜最终分区角色</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜最终上炉温℃</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜最终下炉温℃</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜最终对流风速</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜最终对流配比</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜最终摆动速度</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜最终摆动幅度</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜最终加热时长s</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜目测判级A/B/C</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜为什么这么调</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>★填这里｜成因标签(未定留空)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜是否真值</t>
+        </is>
+      </c>
+      <c r="AK2" s="1" t="inlineStr">
+        <is>
+          <t>勿动｜重复组号</t>
+        </is>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>出炉后补｜实测判级</t>
+        </is>
+      </c>
+      <c r="AM2" s="3" t="inlineStr">
+        <is>
+          <t>出炉后补｜实测能耗kWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>示例-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>2026-07-02T09:30</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>line1/早班</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>clear</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>high_quality</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>炉温稳定</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>700;705;700</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>center;center;edge</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>690</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>705;708;700</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>center;center;edge</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>690</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD3" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>边缘偏低，升边缘温+延时</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr">
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>示例-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>2026-07-02T10:05</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>line1/早班</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>ultra_clear</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>high_efficiency</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>换批次首片</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>700;705;700</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>center;center;edge</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>690</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>700;705;700</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>center;center;edge</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>690</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD4" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>沿用基准即可</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr">
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ultra_clear,clear"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G3:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"high_quality,high_efficiency"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG3:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AL3:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K3:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AJ3:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -975,7 +1226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,15 +1237,20 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>中文名</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>组</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>含义/单位/允许值</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>谁填</t>
         </is>
@@ -1008,15 +1264,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>样本号</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>A 标识</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>唯一样本号</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>记录员</t>
         </is>
@@ -1030,15 +1291,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>A 标识</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>ISO 时间 2026-07-02T09:30</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
@@ -1052,15 +1318,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>工号</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>A 标识</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>老师傅工号（测标签一致性）</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>记录员</t>
         </is>
@@ -1074,15 +1345,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>产线/班次</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>A 标识</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>产线/班次</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>记录员</t>
         </is>
@@ -1096,15 +1372,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>厚度mm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>B 规格·分桶键</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>厚度 mm</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>记录员</t>
         </is>
@@ -1118,15 +1399,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>B 规格·分桶键</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>品类 {ultra_clear,clear}</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>记录员</t>
         </is>
@@ -1140,15 +1426,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>质量模式</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>B 规格·分桶键</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>模式 {high_quality,high_efficiency}</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>记录员</t>
         </is>
@@ -1162,15 +1453,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>X0.95(nm)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>C 输入·状况X</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>应力斑 X0.95，nm（可得则填）</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
@@ -1184,15 +1480,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>IsoT%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>C 输入·状况X</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>IsoT %（暂无→留空/TODO(plant)）</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
@@ -1206,15 +1507,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>CCP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>C 输入·状况X</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>CCP（暂无→留空/TODO(plant)）</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
@@ -1228,15 +1534,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>CCP已标定</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>C 输入·状况X</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>CCP 是否标定 TRUE/FALSE</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
@@ -1250,15 +1561,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>应力斑图路径</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>C 输入·状况X</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>应力斑图路径（有则填）</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
@@ -1272,15 +1588,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>图像哈希</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>C 输入·状况X</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>图像 sha256（有则填）</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
@@ -1294,15 +1615,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>工况备注</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>C 输入·状况X</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>工况备注（结构化字段待定→先文本）</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>记录员</t>
         </is>
@@ -1316,15 +1642,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>基准分区温度℃</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>D 基准(只读参考)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>基准分区温度 ℃，分号隔</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>系统预填</t>
         </is>
@@ -1338,15 +1669,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>基准分区角色</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>D 基准(只读参考)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>基准分区角色，分号隔 {center,edge,...}</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>系统预填</t>
         </is>
@@ -1360,15 +1696,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>基准上炉温℃</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>D 基准(只读参考)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>基准上炉温 ℃</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>系统预填</t>
         </is>
@@ -1382,15 +1723,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>基准下炉温℃</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>D 基准(只读参考)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>基准下炉温 ℃</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>系统预填</t>
         </is>
@@ -1404,15 +1750,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>基准对流风速</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>D 基准(只读参考)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>基准对流风速</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>系统预填</t>
         </is>
@@ -1426,15 +1777,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>基准对流配比</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>D 基准(只读参考)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>基准上下对流配比</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>系统预填</t>
         </is>
@@ -1448,15 +1804,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>基准摆动速度</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>D 基准(只读参考)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>基准摆动速度</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>系统预填</t>
         </is>
@@ -1470,15 +1831,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>基准摆动幅度</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>D 基准(只读参考)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>基准摆动幅度</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>系统预填</t>
         </is>
@@ -1492,15 +1858,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>基准加热时长s</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>D 基准(只读参考)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>基准加热时长 s</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>系统预填</t>
         </is>
@@ -1514,15 +1885,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>最终分区温度℃</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>E 老师傅最终参数</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>最终分区温度 ℃，分号隔（预填=基准，改需动的）</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1536,15 +1912,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>最终分区角色</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>E 老师傅最终参数</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>最终分区角色，分号隔（与温度等长）</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1558,15 +1939,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>最终上炉温℃</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>E 老师傅最终参数</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>最终上炉温 ℃</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1580,15 +1966,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>最终下炉温℃</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>E 老师傅最终参数</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>最终下炉温 ℃</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1602,15 +1993,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>最终对流风速</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>E 老师傅最终参数</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>最终对流风速</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1624,15 +2020,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>最终对流配比</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>E 老师傅最终参数</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>最终上下对流配比</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1646,15 +2047,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>最终摆动速度</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>E 老师傅最终参数</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>最终摆动速度</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1668,15 +2074,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>最终摆动幅度</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>E 老师傅最终参数</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>最终摆动幅度</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1690,15 +2101,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>最终加热时长s</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>E 老师傅最终参数</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>最终加热时长 s</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1712,15 +2128,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>目测判级A/B/C</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>F 主观判级</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>老师傅目测判级 {A,B,C}（≠实测）</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1734,15 +2155,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>为什么这么调</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>G 归因</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>中文理由：为什么这么调</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1756,15 +2182,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>成因标签(未定留空)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>G 归因</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>成因标签（类目未定→留空）</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>老师傅</t>
         </is>
@@ -1778,15 +2209,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>是否真值</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>H 复核·一致性</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>是否专家真值 TRUE/FALSE（默认 TRUE）</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>记录员</t>
         </is>
@@ -1800,15 +2236,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>重复组号</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>H 复核·一致性</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>重复标注组号（隔时重标同一情形用同号）</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>记录员</t>
         </is>
@@ -1822,15 +2263,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>实测判级</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>I outcome(出炉后补)</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>实测质量判级 {A,B,C}（现在留空）</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>后补</t>
         </is>
@@ -1844,15 +2290,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>实测能耗kWh</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>I outcome(出炉后补)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>实测能耗 kWh（现在留空）</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>后补</t>
         </is>

--- a/data/annotation/标注表模板.xlsx
+++ b/data/annotation/标注表模板.xlsx
@@ -27,7 +27,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -35,7 +35,7 @@
     <font/>
     <font>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
     </font>
   </fonts>
   <fills count="5">
@@ -47,17 +47,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -445,7 +445,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AM4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="14" customWidth="1" min="2" max="4"/>

--- a/data/annotation/标注表模板.xlsx
+++ b/data/annotation/标注表模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="标注表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="字段字典" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标注表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>ultra_clear</t>
+          <t>low_e</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="F3:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ultra_clear,clear"</formula1>
+      <formula1>"ultra_clear,clear,low_e,coated,enameled,patterned,other"</formula1>
     </dataValidation>
     <dataValidation sqref="G3:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"high_quality,high_efficiency"</formula1>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>品类 {ultra_clear,clear}</t>
+          <t>品类 {普白clear,超白ultra_clear,Low-E low_e,镀膜coated,彩釉enameled,压花patterned,其他other}</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
